--- a/Apostas_Diarias/Apostas_20260418.xlsx
+++ b/Apostas_Diarias/Apostas_20260418.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F95E642097980C1F05007B83479C7FA3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150FE50E-F89F-4037-9BD6-DDBFF5A5A990}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F9546C9566522C1F050EC90747AD1E287" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF5430F-1213-47FC-BD0D-C2447D5FBE03}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>Data</t>
   </si>
@@ -74,37 +74,70 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
-    <t>SLOVAKIA 1</t>
-  </si>
-  <si>
-    <t>Podbrezova x Dunajska Streda</t>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>FINLAND 1</t>
+  </si>
+  <si>
+    <t>Jaro x KuPS</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>Ruzomberok x KFC Komarno</t>
-  </si>
-  <si>
     <t>11:00:00</t>
   </si>
   <si>
     <t>SCOTLAND 2</t>
   </si>
   <si>
-    <t>Ross Co x Ayr</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>FK Novi Pazar x OFK Beograd</t>
+    <t>Airdrieonians x Partick</t>
+  </si>
+  <si>
+    <t>TPS x SJK</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>IFK Mariehamn x Ilves</t>
+  </si>
+  <si>
+    <t>13:15:00</t>
+  </si>
+  <si>
+    <t>WALES 1</t>
+  </si>
+  <si>
+    <t>Barry Town Utd x The New Saints</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>TURKEY 1</t>
+  </si>
+  <si>
+    <t>Genclerbirligi x Galatasaray</t>
+  </si>
+  <si>
+    <t>PORTUGAL 2</t>
+  </si>
+  <si>
+    <t>Torreense x Maritimo</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>FRANCE 2</t>
+  </si>
+  <si>
+    <t>Bastia x St Etienne</t>
   </si>
 </sst>
 </file>
@@ -444,14 +477,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -494,6 +527,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -515,12 +551,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="H2">
-        <v>12.5</v>
+        <f>G2</f>
+        <v>9.4</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -529,7 +567,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>40.652173913043484</v>
+        <v>55.654761904761905</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -543,33 +581,35 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <f t="shared" ref="H3:H9" si="0">G3</f>
+        <v>10</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I9" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J5" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J9" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K5" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>42.5</v>
+        <f t="shared" ref="K3:K9" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>51.944444444444443</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -583,10 +623,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -595,21 +635,23 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H4">
-        <v>12.5</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -626,32 +668,202 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="H5">
-        <v>13.5</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>10.5</v>
+      </c>
+      <c r="H6">
         <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="2"/>
+        <v>RED</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
-      <c r="K5">
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>57.01219512195123</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>10.5</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="1"/>
-        <v>37.400000000000006</v>
-      </c>
-      <c r="L5">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>8.6</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>8.6</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>61.513157894736842</v>
+      </c>
+      <c r="L9">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260418.xlsx
+++ b/Apostas_Diarias/Apostas_20260418.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F9546C9566522C1F050EC90747AD1E287" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF5430F-1213-47FC-BD0D-C2447D5FBE03}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F95E642097980C1F05007B83479C7FA3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150FE50E-F89F-4037-9BD6-DDBFF5A5A990}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -74,70 +74,37 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
-    <t>FINLAND 1</t>
-  </si>
-  <si>
-    <t>Jaro x KuPS</t>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>SLOVAKIA 1</t>
+  </si>
+  <si>
+    <t>Podbrezova x Dunajska Streda</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
+    <t>Ruzomberok x KFC Komarno</t>
+  </si>
+  <si>
     <t>11:00:00</t>
   </si>
   <si>
     <t>SCOTLAND 2</t>
   </si>
   <si>
-    <t>Airdrieonians x Partick</t>
-  </si>
-  <si>
-    <t>TPS x SJK</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>IFK Mariehamn x Ilves</t>
-  </si>
-  <si>
-    <t>13:15:00</t>
-  </si>
-  <si>
-    <t>WALES 1</t>
-  </si>
-  <si>
-    <t>Barry Town Utd x The New Saints</t>
-  </si>
-  <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>TURKEY 1</t>
-  </si>
-  <si>
-    <t>Genclerbirligi x Galatasaray</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Torreense x Maritimo</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Bastia x St Etienne</t>
+    <t>Ross Co x Ayr</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>SERBIA 1</t>
+  </si>
+  <si>
+    <t>FK Novi Pazar x OFK Beograd</t>
   </si>
 </sst>
 </file>
@@ -477,14 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -527,9 +494,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -551,14 +515,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -567,7 +529,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>55.654761904761905</v>
+        <v>40.652173913043484</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -581,35 +543,33 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H9" si="0">G3</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I9" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J9" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J5" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K9" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>51.944444444444443</v>
+        <f t="shared" ref="K3:K5" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>42.5</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -623,10 +583,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -635,23 +595,21 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
+        <v>12.5</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>40.652173913043484</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -668,202 +626,32 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="H5">
+        <v>13.5</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I5">
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
+        <v>37.400000000000006</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>10.5</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>-500</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>57.01219512195123</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>10.5</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>8.6</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>8.6</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>61.513157894736842</v>
-      </c>
-      <c r="L9">
         <v>1</v>
       </c>
     </row>
